--- a/marketing_report/outputs/Grado_Pregrado/Analisis_No_Matcheados/datos_analisis_no_matcheados.xlsx
+++ b/marketing_report/outputs/Grado_Pregrado/Analisis_No_Matcheados/datos_analisis_no_matcheados.xlsx
@@ -94,7 +94,7 @@
     <t>0 días</t>
   </si>
   <si>
-    <t>3,255</t>
+    <t>3,205</t>
   </si>
   <si>
     <t>Decil</t>
@@ -139,25 +139,25 @@
     <t>2</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
-    <t>41</t>
+    <t>42</t>
   </si>
   <si>
     <t>99</t>
   </si>
   <si>
-    <t>157</t>
-  </si>
-  <si>
-    <t>213</t>
+    <t>156</t>
+  </si>
+  <si>
+    <t>212</t>
   </si>
   <si>
     <t>342</t>
@@ -6018,16 +6018,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>3549</v>
+        <v>3838</v>
       </c>
       <c r="C2">
-        <v>60.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="D2">
-        <v>203449</v>
+        <v>208804</v>
       </c>
       <c r="E2">
-        <v>81.8</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6035,16 +6035,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>1280</v>
+        <v>1105</v>
       </c>
       <c r="C3">
-        <v>21.7</v>
+        <v>19.6</v>
       </c>
       <c r="D3">
-        <v>32694</v>
+        <v>32603</v>
       </c>
       <c r="E3">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -6052,16 +6052,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>570</v>
+        <v>398</v>
       </c>
       <c r="C4">
-        <v>9.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="D4">
-        <v>8081</v>
+        <v>7705</v>
       </c>
       <c r="E4">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6069,16 +6069,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>232</v>
+        <v>158</v>
       </c>
       <c r="C5">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="D5">
-        <v>2570</v>
+        <v>2388</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -6086,16 +6086,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="C6">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="D6">
-        <v>944</v>
+        <v>815</v>
       </c>
       <c r="E6">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6103,16 +6103,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>414</v>
+        <v>366</v>
       </c>
       <c r="E7">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6120,13 +6120,13 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="D8">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E8">
         <v>0.1</v>
@@ -6137,13 +6137,13 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D9">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6154,13 +6154,13 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D10">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6171,13 +6171,13 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D11">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6188,13 +6188,13 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C12">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D12">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -17908,16 +17908,16 @@
         <v>750</v>
       </c>
       <c r="B699">
-        <v>244013</v>
+        <v>243926</v>
       </c>
       <c r="C699">
-        <v>11868</v>
+        <v>11742</v>
       </c>
       <c r="D699">
-        <v>286219</v>
+        <v>286251</v>
       </c>
       <c r="E699">
-        <v>4.86</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="700" spans="1:5">
@@ -20561,13 +20561,13 @@
         <v>116</v>
       </c>
       <c r="C857">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D857">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E857">
-        <v>5.17</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="858" spans="1:5">
@@ -23054,16 +23054,16 @@
         <v>1058</v>
       </c>
       <c r="B1007">
-        <v>51951</v>
+        <v>51939</v>
       </c>
       <c r="C1007">
-        <v>676</v>
+        <v>653</v>
       </c>
       <c r="D1007">
-        <v>63910</v>
+        <v>63921</v>
       </c>
       <c r="E1007">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="1008" spans="1:5">
@@ -23091,13 +23091,13 @@
         <v>3671</v>
       </c>
       <c r="C1009">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D1009">
-        <v>4409</v>
+        <v>4410</v>
       </c>
       <c r="E1009">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="1010" spans="1:5">
@@ -30305,13 +30305,13 @@
         <v>2760</v>
       </c>
       <c r="C1442">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D1442">
-        <v>3281</v>
+        <v>3283</v>
       </c>
       <c r="E1442">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="1443" spans="1:5">
@@ -34498,16 +34498,16 @@
         <v>1746</v>
       </c>
       <c r="B1695">
-        <v>4366</v>
+        <v>4358</v>
       </c>
       <c r="C1695">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D1695">
-        <v>4372</v>
+        <v>4371</v>
       </c>
       <c r="E1695">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="1696" spans="1:5">
@@ -35946,13 +35946,13 @@
         <v>4668</v>
       </c>
       <c r="C1783">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D1783">
-        <v>5756</v>
+        <v>5757</v>
       </c>
       <c r="E1783">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="1784" spans="1:5">
